--- a/open-wo-tracker/Open_WOs_tracker.xlsx
+++ b/open-wo-tracker/Open_WOs_tracker.xlsx
@@ -45,7 +45,7 @@
     <numFmt numFmtId="166" formatCode="&quot;▲ &quot;#,##0;&quot;▼ &quot;#,##0;&quot;no change&quot;"/>
     <numFmt numFmtId="167" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -96,6 +96,12 @@
       <name val="Calibri"/>
       <color rgb="FF6A6A66"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF6A6A66"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -276,33 +282,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -323,38 +329,38 @@
     <xf numFmtId="166" fontId="2" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -400,24 +406,25 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1928,7 +1935,7 @@
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3">
-        <f>IF($N$1=0,"No weeks entered yet — start on the Totals tab.","Week of "&amp;TEXT($N$2,"mmmm d, yyyy")&amp;":   "&amp;TEXT($D$8,"#,##0")&amp;" open repair tickets"&amp;IF($F$8=""," (first week on record)"," ("&amp;IF($F$8&gt;0,"up "&amp;TEXT($F$8,"#,##0"),IF($F$8&lt;0,"down "&amp;TEXT(-$F$8,"#,##0"),"unchanged"))&amp;" "&amp;$N$7&amp;")")&amp;".   PMs "&amp;TEXT($D$12,"#,##0")&amp;IF($F$12=""," "," ("&amp;IF($F$12&gt;0,"up "&amp;TEXT($F$12,"#,##0"),IF($F$12&lt;0,"down "&amp;TEXT(-$F$12,"#,##0"),"unchanged"))&amp;").")&amp;"   All open "&amp;TEXT($D$16,"#,##0")&amp;".")</f>
+        <f>IF($N$1=0,"No weeks entered yet — start on the Totals tab.","Week of "&amp;TEXT($N$2,"mmmm d, yyyy")&amp;":   "&amp;TEXT($D$8,"#,##0")&amp;" open repair tickets"&amp;IF($F$8=""," (first week on record)"," ("&amp;IF($F$8&gt;0,"up "&amp;TEXT($F$8,"#,##0"),IF($F$8&lt;0,"down "&amp;TEXT(-$F$8,"#,##0"),"unchanged"))&amp;" "&amp;$N$7&amp;")")&amp;".   PMs "&amp;TEXT($D$12,"#,##0")&amp;IF($F$12="","."," ("&amp;IF($F$12&gt;0,"up "&amp;TEXT($F$12,"#,##0"),IF($F$12&lt;0,"down "&amp;TEXT(-$F$12,"#,##0"),"unchanged"))&amp;").")&amp;"   All open "&amp;TEXT($D$16,"#,##0")&amp;".")</f>
         <v/>
       </c>
       <c r="N3">
@@ -2275,7 +2282,7 @@
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="F37" s="20">
-        <f>IF($N$1=0,"Enter a week on the Totals tab and this fills in.","Open work orders — week of "&amp;TEXT($N$2,"mm/dd/yyyy")&amp;CHAR(10)&amp;CHAR(10)&amp;"Repair tickets: "&amp;TEXT($D$8,"#,##0")&amp;"  ("&amp;IF($F$8="","n/a",IF($F$8&gt;0,"+"&amp;TEXT($F$8,"#,##0"),IF($F$8&lt;0,TEXT($F$8,"#,##0"),"no change")))&amp;" "&amp;$N$7&amp;")"&amp;CHAR(10)&amp;"PMs: "&amp;TEXT($D$12,"#,##0")&amp;"  ("&amp;IF($F$12="","n/a",IF($F$12&gt;0,"+"&amp;TEXT($F$12,"#,##0"),IF($F$12&lt;0,TEXT($F$12,"#,##0"),"no change")))&amp;")"&amp;CHAR(10)&amp;"All open: "&amp;TEXT($D$16,"#,##0")&amp;"  ("&amp;IF($F$16="","n/a",IF($F$16&gt;0,"+"&amp;TEXT($F$16,"#,##0"),IF($F$16&lt;0,TEXT($F$16,"#,##0"),"no change")))&amp;")"&amp;CHAR(10)&amp;CHAR(10)&amp;"Burnsville: "&amp;TEXT($D$14,"#,##0")&amp;"  ("&amp;IF($F$14="","n/a",IF($F$14&gt;0,"+"&amp;TEXT($F$14,"#,##0"),IF($F$14&lt;0,TEXT($F$14,"#,##0"),"no change")))&amp;")"&amp;CHAR(10)&amp;"Lakeville: "&amp;TEXT($D$15,"#,##0")&amp;"  ("&amp;IF($F$15="","n/a",IF($F$15&gt;0,"+"&amp;TEXT($F$15,"#,##0"),IF($F$15&lt;0,TEXT($F$15,"#,##0"),"no change")))&amp;")"&amp;CHAR(10)&amp;CHAR(10)&amp;"Full history and charts: "&amp;$N$5)</f>
+        <f>IF($N$1=0,"Enter a week on the Totals tab and this fills in.","Open work orders — week of "&amp;TEXT($N$2,"mm/dd/yyyy")&amp;CHAR(10)&amp;CHAR(10)&amp;"Repair tickets: "&amp;TEXT($D$8,"#,##0")&amp;"  ("&amp;IF($F$8="","n/a",IF($F$8&gt;0,"+"&amp;TEXT($F$8,"#,##0"),IF($F$8&lt;0,TEXT($F$8,"#,##0"),"no change")))&amp;IF($N$7="",""," "&amp;$N$7)&amp;")"&amp;CHAR(10)&amp;"PMs: "&amp;TEXT($D$12,"#,##0")&amp;"  ("&amp;IF($F$12="","n/a",IF($F$12&gt;0,"+"&amp;TEXT($F$12,"#,##0"),IF($F$12&lt;0,TEXT($F$12,"#,##0"),"no change")))&amp;")"&amp;CHAR(10)&amp;"All open: "&amp;TEXT($D$16,"#,##0")&amp;"  ("&amp;IF($F$16="","n/a",IF($F$16&gt;0,"+"&amp;TEXT($F$16,"#,##0"),IF($F$16&lt;0,TEXT($F$16,"#,##0"),"no change")))&amp;")"&amp;CHAR(10)&amp;CHAR(10)&amp;"Burnsville: "&amp;TEXT($D$14,"#,##0")&amp;"  ("&amp;IF($F$14="","n/a",IF($F$14&gt;0,"+"&amp;TEXT($F$14,"#,##0"),IF($F$14&lt;0,TEXT($F$14,"#,##0"),"no change")))&amp;")"&amp;CHAR(10)&amp;"Lakeville: "&amp;TEXT($D$15,"#,##0")&amp;"  ("&amp;IF($F$15="","n/a",IF($F$15&gt;0,"+"&amp;TEXT($F$15,"#,##0"),IF($F$15&lt;0,TEXT($F$15,"#,##0"),"no change")))&amp;")"&amp;CHAR(10)&amp;CHAR(10)&amp;"Full history and charts: "&amp;$N$5)</f>
         <v/>
       </c>
       <c r="G37" s="21" t="n"/>
@@ -17376,6 +17383,13 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>Rows 30–35 below are hidden. They hold the bookkeeping that puts each week on the History tab — leave them alone.</t>
+        </is>
+      </c>
+    </row>
     <row r="30" hidden="1">
       <c r="A30">
         <f>IF(AND(A$1="DATE",ISNUMBER(B$1),COUNT(A4,A5,A9,A10)=4),1,0)</f>
@@ -25414,7 +25428,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="531">
+  <mergeCells count="532">
     <mergeCell ref="KA15:KB15"/>
     <mergeCell ref="DZ8:EA8"/>
     <mergeCell ref="HP1:HQ1"/>
@@ -25713,6 +25727,7 @@
     <mergeCell ref="BD15:BE15"/>
     <mergeCell ref="EA15:EB15"/>
     <mergeCell ref="ES1:ET1"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="EM1:EN1"/>
     <mergeCell ref="N15:O15"/>
     <mergeCell ref="AF1:AG1"/>
@@ -25949,12 +25964,12 @@
   </mergeCells>
   <conditionalFormatting sqref="A4:OJ5">
     <cfRule type="expression" priority="1" dxfId="3" stopIfTrue="0">
-      <formula>AND(A$1="DATE",ISBLANK(A4),INDEX($A$1:$OJ$1,COLUMN()+1)+5&lt;=TODAY())</formula>
+      <formula>AND(A$1="DATE",ISBLANK(A4),ISNUMBER(INDEX($A$1:$OJ$1,COLUMN()+1)),INDEX($A$1:$OJ$1,COLUMN()+1)+5&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9:OJ10">
     <cfRule type="expression" priority="2" dxfId="3" stopIfTrue="0">
-      <formula>AND(A$1="DATE",ISBLANK(A9),INDEX($A$1:$OJ$1,COLUMN()+1)+5&lt;=TODAY())</formula>
+      <formula>AND(A$1="DATE",ISBLANK(A9),ISNUMBER(INDEX($A$1:$OJ$1,COLUMN()+1)),INDEX($A$1:$OJ$1,COLUMN()+1)+5&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:OJ1">
@@ -25992,7 +26007,7 @@
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>OPEN WORK ORDERS TRACKER — READ ME</t>
         </is>
@@ -26007,14 +26022,14 @@
       <c r="C4" s="18" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="44" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>One row per week showing how many work orders are open at Burnsville and at Lakeville, split into repair tickets and PMs. It answers the standing question: is the backlog growing or shrinking?</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>You type four numbers a week, on the Totals tab. Everything else — totals, the change since the last entry, the charts, the scorecard and the email text — is calculated. The History tab is the one you send.</t>
         </is>
@@ -26030,72 +26045,72 @@
       <c r="C8" s="18" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="45" t="inlineStr">
         <is>
           <t>Pull the open work order counts for both plants.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="C10" s="44" t="inlineStr">
+      <c r="C10" s="45" t="inlineStr">
         <is>
           <t>Open the Totals tab. The link under the grid jumps to the block whose date is this week.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1">
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>Step 3</t>
         </is>
       </c>
-      <c r="C11" s="44" t="inlineStr">
+      <c r="C11" s="45" t="inlineStr">
         <is>
           <t>Type all four counts into the blue cells: repair tickets and PMs for Burnsville, then the same two for Lakeville. A week is only picked up once all four are in, so a half-filled block is left out rather than reported as zeros.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>Step 4</t>
         </is>
       </c>
-      <c r="C12" s="44" t="inlineStr">
+      <c r="C12" s="45" t="inlineStr">
         <is>
           <t>If a number moved for a reason worth remembering, type it into the NOTE row of that same block. It shows up in the Notes column of the weekly log.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="45" t="inlineStr">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>Step 5</t>
         </is>
       </c>
-      <c r="C13" s="44" t="inlineStr">
+      <c r="C13" s="45" t="inlineStr">
         <is>
           <t>Go to the History tab and read the top. If a red bar has appeared under the headline, fix what it names before you send anything.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>Step 6</t>
         </is>
       </c>
-      <c r="C14" s="44" t="inlineStr">
+      <c r="C14" s="45" t="inlineStr">
         <is>
           <t>Copy the email box (to the right of the charts) into your weekly email. In Outlook, paste with Keep Text Only, or you will paste a one-cell table. Send the file link with it.</t>
         </is>
@@ -26111,42 +26126,42 @@
       <c r="C16" s="18" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>Repair tickets and PMs are counted separately on purpose. PMs are scheduled work: when the maintenance system releases a new batch, the PM count jumps by dozens overnight without anything going wrong on the floor.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="44" t="inlineStr">
+      <c r="B18" s="45" t="inlineStr">
         <is>
           <t>Repair tickets are the number that reflects real, unplanned backlog. When you are asked whether things are getting better or worse, that is the line to look at.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="60" customHeight="1">
-      <c r="B19" s="44" t="inlineStr">
+      <c r="B19" s="45" t="inlineStr">
         <is>
           <t>▲ means more open than the previous entry, ▼ means fewer. The arrow carries the meaning, so it reads correctly in black and white and for a colourblind reader. Only the repair rows are coloured red and green, because a rising PM count usually means a batch was released, not that anything went wrong.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="44" t="inlineStr">
+      <c r="B20" s="45" t="inlineStr">
         <is>
           <t>The 4-week average column answers "is this week normal?". A single week bounces around; the average is what tells you whether the level has actually moved.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="60" customHeight="1">
-      <c r="B21" s="44" t="inlineStr">
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>There is one chart per plant, plus one for the two together. They are split that way because Lakeville runs about twenty times higher than Burnsville: any chart holding both plants' PM counts would flatten Burnsville onto the axis and show nothing. In every chart blue is repair tickets, orange is PMs, and dark grey is the two added together.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="44" t="inlineStr">
+      <c r="B22" s="45" t="inlineStr">
         <is>
           <t>The charts show the most recent 26 weeks so they stay readable as the file fills up. Every week ever recorded is in the log underneath them.</t>
         </is>
@@ -26162,21 +26177,21 @@
       <c r="C24" s="18" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="44" t="inlineStr">
+      <c r="B25" s="45" t="inlineStr">
         <is>
           <t>"Count Date" is the date the count was actually pulled, which is normally a Monday. The first entry, 09-15-2026, was pulled on a Tuesday and is left as it was recorded rather than tidied.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="45" t="inlineStr">
         <is>
           <t>A count is the number of work orders open at the moment of the pull, not the number opened or closed that week.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
-      <c r="B27" s="44" t="inlineStr">
+      <c r="B27" s="45" t="inlineStr">
         <is>
           <t>Leave a week blank if no count was taken. The history skips it rather than showing a zero. Because of that, "Change vs Previous Entry" compares against the last week actually recorded, which is not always seven days back — the headline and the email say how long ago it really was.</t>
         </is>
@@ -26192,60 +26207,60 @@
       <c r="C29" s="18" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="45" t="inlineStr">
+      <c r="B30" s="46" t="inlineStr">
         <is>
           <t>Blue on Totals</t>
         </is>
       </c>
-      <c r="C30" s="44" t="inlineStr">
+      <c r="C30" s="45" t="inlineStr">
         <is>
           <t>Cells you type into: the four counts and the NOTE. Nothing else on Totals is typed.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="45" t="inlineStr">
+      <c r="B31" s="46" t="inlineStr">
         <is>
           <t>Yellow fill</t>
         </is>
       </c>
-      <c r="C31" s="44" t="inlineStr">
+      <c r="C31" s="45" t="inlineStr">
         <is>
           <t>Something is missing: a week whose date has passed with no counts entered, or a blank you are expected to fill in on this tab.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="45" t="inlineStr">
+      <c r="B32" s="46" t="inlineStr">
         <is>
           <t>Red fill on a date</t>
         </is>
       </c>
-      <c r="C32" s="44" t="inlineStr">
+      <c r="C32" s="45" t="inlineStr">
         <is>
           <t>Two blocks carry that same date. Fix it — one of them is a duplicate and will publish a week that never happened.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="45" t="inlineStr">
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t>Red bar on History</t>
         </is>
       </c>
-      <c r="C33" s="44" t="inlineStr">
+      <c r="C33" s="45" t="inlineStr">
         <is>
           <t>A problem worth stopping for. The bar says what it is. When everything is fine there is no bar.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="45" t="inlineStr">
+      <c r="B34" s="46" t="inlineStr">
         <is>
           <t>Black numbers</t>
         </is>
       </c>
-      <c r="C34" s="44" t="inlineStr">
+      <c r="C34" s="45" t="inlineStr">
         <is>
           <t>Calculated. Do not type over them — you would break the week.</t>
         </is>
@@ -26261,20 +26276,20 @@
       <c r="C36" s="18" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="B37" s="46" t="inlineStr">
+      <c r="B37" s="47" t="inlineStr">
         <is>
           <t>Where this file lives (paste the SharePoint link)</t>
         </is>
       </c>
-      <c r="C37" s="47" t="inlineStr"/>
+      <c r="C37" s="48" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="46" t="inlineStr">
+      <c r="B38" s="47" t="inlineStr">
         <is>
           <t>Name of the report the counts come from</t>
         </is>
       </c>
-      <c r="C38" s="47" t="inlineStr"/>
+      <c r="C38" s="48" t="inlineStr"/>
     </row>
     <row r="39" ht="8" customHeight="1"/>
     <row r="40" ht="22" customHeight="1">
@@ -26286,14 +26301,14 @@
       <c r="C40" s="18" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="44" t="inlineStr">
+      <c r="B41" s="45" t="inlineStr">
         <is>
           <t>The three tabs are protected with no password, so you can still type in the blue cells and the yellow ones and nowhere else. It is a guard rail against overtyping a formula, not a lock.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="45" customHeight="1">
-      <c r="B42" s="44" t="inlineStr">
+      <c r="B42" s="45" t="inlineStr">
         <is>
           <t>If you genuinely need to change something else — adding rows to the log, or adding blocks past the pre-built ones — use Review &gt; Unprotect Sheet, make the change, then Review &gt; Protect Sheet to put it back.</t>
         </is>
@@ -26309,28 +26324,28 @@
       <c r="C44" s="18" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="B45" s="44" t="inlineStr">
+      <c r="B45" s="45" t="inlineStr">
         <is>
           <t>Do not sort or re-order the weekly log. Every cell in it is a formula tied to its week, so sorting would scramble it. The filter buttons have been removed for that reason.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="B46" s="44" t="inlineStr">
+      <c r="B46" s="45" t="inlineStr">
         <is>
           <t>Do not type into the weekly log, including the Notes column. Notes belong on the Totals tab, in the NOTE row of the week they describe, so they stay attached to that week no matter what else changes.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="B47" s="44" t="inlineStr">
+      <c r="B47" s="45" t="inlineStr">
         <is>
           <t>Do not give two blocks the same date. That is the one mistake that produces a believable but wrong number, so the file watches for it and says so.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="B48" s="44" t="inlineStr">
+      <c r="B48" s="45" t="inlineStr">
         <is>
           <t>Do not insert a column inside an existing block. Adding whole blocks on the right is safe; splitting one is not.</t>
         </is>
@@ -26346,35 +26361,35 @@
       <c r="C50" s="18" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="B51" s="44" t="inlineStr">
+      <c r="B51" s="45" t="inlineStr">
         <is>
           <t>Blocks are pre-built through September 11, 2028, and the weekly log has room for 110 weeks. That is about two years from the first entry.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="45" customHeight="1">
-      <c r="B52" s="44" t="inlineStr">
+      <c r="B52" s="45" t="inlineStr">
         <is>
           <t>To add a week: select the three columns of the last block, copy, paste into the next three empty columns to the right, then DELETE the four counts and the note, and only then change the date. Clearing before dating is what stops a duplicate week appearing. Do not paste past column OJ.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="B53" s="44" t="inlineStr">
+      <c r="B53" s="45" t="inlineStr">
         <is>
           <t>To add rows to the log: click the last row of the weekly log and drag the fill handle down. Every column is a formula and will copy.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="B54" s="44" t="inlineStr">
+      <c r="B54" s="45" t="inlineStr">
         <is>
           <t>Hidden rows 30 to 35 on Totals do the block bookkeeping and the error checking. Leave them alone; unhide them if you ever need to see why a week is not appearing.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="45" customHeight="1">
-      <c r="B55" s="44" t="inlineStr">
+      <c r="B55" s="45" t="inlineStr">
         <is>
           <t>Every formula in this file uses functions that have been in Excel since 2007, so it opens the same in Excel for the web, on a phone, and in older desktop versions. If you edit it, keep to those — newer functions can come back as #NAME? for other people.</t>
         </is>
@@ -26390,56 +26405,56 @@
       <c r="C57" s="18" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="48" t="inlineStr">
+      <c r="B58" s="49" t="inlineStr">
         <is>
           <t>Weeks recorded</t>
         </is>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="50">
         <f>History!$N$1</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="48" t="inlineStr">
+      <c r="B59" s="49" t="inlineStr">
         <is>
           <t>Blocks built on Totals</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>Totals!$C$33</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="48" t="inlineStr">
+      <c r="B60" s="49" t="inlineStr">
         <is>
           <t>Part-filled blocks being skipped</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>Totals!$E$33</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="48" t="inlineStr">
+      <c r="B61" s="49" t="inlineStr">
         <is>
           <t>Blocks sharing a date</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>Totals!$F$33</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="48" t="inlineStr">
+      <c r="B62" s="49" t="inlineStr">
         <is>
           <t>Blocks the History tab can see</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(Totals!$D$33&gt;Totals!$C$33,"PROBLEM: blocks exist past column OJ and are being ignored","all of them")</f>
         <v/>
       </c>
@@ -26454,14 +26469,14 @@
       <c r="C64" s="18" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="B65" s="44" t="inlineStr">
+      <c r="B65" s="45" t="inlineStr">
         <is>
           <t>2026-09-21 — first version: Totals entry grid plus a weekly history tab.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="75" customHeight="1">
-      <c r="B66" s="44" t="inlineStr">
+      <c r="B66" s="45" t="inlineStr">
         <is>
           <t>2026-09-22 — rebuilt. Added the scorecard at the top with repair tickets as the headline and a 4-week average, split repair tickets from PMs, replaced the single chart with one per plant over a rolling 26 weeks, moved notes onto the Totals blocks so they cannot drift off their week, added the email box, this tab, two years of pre-built weeks, checks for part-filled and duplicate weeks, sheet protection, and block lookup that no longer depends on counting columns.</t>
         </is>
